--- a/data/site_config.xlsx
+++ b/data/site_config.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,7 +412,7 @@
         <v>hero_title</v>
       </c>
       <c r="B2" t="str">
-        <v>1111</v>
+        <v>NeuralForge · 神经锻造厂</v>
       </c>
     </row>
     <row r="3">
@@ -420,7 +420,7 @@
         <v>hero_subtitle</v>
       </c>
       <c r="B3" t="str">
-        <v>2222</v>
+        <v>Crafting immersive experiences at the intersection of game development and artificial intelligence</v>
       </c>
     </row>
     <row r="4">
@@ -428,7 +428,7 @@
         <v>about_me</v>
       </c>
       <c r="B4" t="str">
-        <v>333</v>
+        <v>I am a passionate developer specializing in Unity game development and AI technologies. With expertise in both fields, I create innovative projects that push the boundaries of interactive experiences.</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>avatar_url</v>
       </c>
       <c r="B5" t="str">
-        <v>/uploads/1780333897880-166682085.png</v>
+        <v>/uploads/config/1780539910209-892760956.webp</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         <v>email</v>
       </c>
       <c r="B6" t="str">
-        <v>3348066149@qq.com</v>
+        <v>3349@qq.com</v>
       </c>
     </row>
     <row r="7">
@@ -460,12 +460,36 @@
         <v>linkedin_url</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.deepseek.com/</v>
+        <v>https://linkedin.com</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>wechat_image_url</v>
+      </c>
+      <c r="B9" t="str">
+        <v>/uploads/config/1780539910209-485512251.jpg</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>wechat_text</v>
+      </c>
+      <c r="B10" t="str">
+        <v>有兴趣加我v</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>bilibili_url</v>
+      </c>
+      <c r="B11" t="str">
+        <v>https://bilibili.com</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/site_config.xlsx
+++ b/data/site_config.xlsx
@@ -420,7 +420,7 @@
         <v>hero_subtitle</v>
       </c>
       <c r="B3" t="str">
-        <v>Crafting immersive experiences at the intersection of game development and artificial intelligence</v>
+        <v>不等到很厉害了再开始  而是开始了才会变厉害</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +444,7 @@
         <v>email</v>
       </c>
       <c r="B6" t="str">
-        <v>3349@qq.com</v>
+        <v>3348066149@qq.com</v>
       </c>
     </row>
     <row r="7">
@@ -452,7 +452,7 @@
         <v>github_url</v>
       </c>
       <c r="B7" t="str">
-        <v>https://github.com</v>
+        <v>https://github.com/3348066149</v>
       </c>
     </row>
     <row r="8">
@@ -460,7 +460,7 @@
         <v>linkedin_url</v>
       </c>
       <c r="B8" t="str">
-        <v>https://linkedin.com</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -484,7 +484,7 @@
         <v>bilibili_url</v>
       </c>
       <c r="B11" t="str">
-        <v>https://bilibili.com</v>
+        <v>https://space.bilibili.com/389373658?spm_id_from=333.1007.0.0</v>
       </c>
     </row>
   </sheetData>
